--- a/exports/colleges/25494_iima-indian-institute-of-management-ahmedabad.xlsx
+++ b/exports/colleges/25494_iima-indian-institute-of-management-ahmedabad.xlsx
@@ -433,7 +433,7 @@
     <col width="16" customWidth="1" min="7" max="7"/>
     <col width="16" customWidth="1" min="8" max="8"/>
     <col width="12" customWidth="1" min="9" max="9"/>
-    <col width="12" customWidth="1" min="10" max="10"/>
+    <col width="13" customWidth="1" min="10" max="10"/>
     <col width="12" customWidth="1" min="11" max="11"/>
     <col width="12" customWidth="1" min="12" max="12"/>
     <col width="169" customWidth="1" min="13" max="13"/>
@@ -558,7 +558,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>#2</t>
+          <t>CD Rank #2</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -593,11 +593,21 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B2"/>
+  <dimension ref="A1:L5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
-    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="74" customWidth="1" min="3" max="3"/>
+    <col width="74" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="16" customWidth="1" min="8" max="8"/>
+    <col width="16" customWidth="1" min="9" max="9"/>
+    <col width="19" customWidth="1" min="10" max="10"/>
+    <col width="16" customWidth="1" min="11" max="11"/>
+    <col width="15" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -608,7 +618,57 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>status</t>
+          <t>degree_name</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>course_name</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>specialization</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>total_fees</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>duration</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>course_type</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>eligibility</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>entrance_exam</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>application_date</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>intake_seats</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>course_level</t>
         </is>
       </c>
     </row>
@@ -620,7 +680,243 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>No Data Available</t>
+          <t>MBA</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Post Graduate Programme in Food and Agri-Business Management [PGP-FABM]</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Post Graduate Programme in Food and Agri-Business Management [PGP-FABM]</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>27.5 Lakhs</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>PG</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>25494</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>MBA</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Master of Business Administration [MBA]</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Master of Business Administration [MBA]</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>20 Lakhs</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>PG</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>25494</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Ph.D</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Ph.D. (Management)</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Ph.D. (Management)</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>PG</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>25494</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>MBA</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Post Graduate Programme in Management [PGPM]</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Post Graduate Programme in Management [PGPM]</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>27.5 Lakhs</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>PG</t>
         </is>
       </c>
     </row>
@@ -729,7 +1025,7 @@
     <col width="18" customWidth="1" min="3" max="3"/>
     <col width="17" customWidth="1" min="4" max="4"/>
     <col width="23" customWidth="1" min="5" max="5"/>
-    <col width="17" customWidth="1" min="6" max="6"/>
+    <col width="73" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -772,17 +1068,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>1.32 Cr</t>
+          <t>1.15 CPA</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>27.60 LPA</t>
+          <t>35.07 LPA</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>36.2 LPA</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -792,7 +1088,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>Microsoft, Google, Accenture, TCS, Wipro, HCL, Goldman Sachs, Flipkart</t>
         </is>
       </c>
     </row>
@@ -812,7 +1108,7 @@
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
     <col width="15" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
     <col width="15" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
@@ -851,12 +1147,10 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>#1</t>
-        </is>
-      </c>
-      <c r="D2" t="n">
-        <v>2025</v>
-      </c>
+          <t>CD Rank #2</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/exports/colleges/25494_iima-indian-institute-of-management-ahmedabad.xlsx
+++ b/exports/colleges/25494_iima-indian-institute-of-management-ahmedabad.xlsx
@@ -593,18 +593,18 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L5"/>
+  <dimension ref="A1:L6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="33" customWidth="1" min="2" max="2"/>
     <col width="74" customWidth="1" min="3" max="3"/>
     <col width="74" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
-    <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
     <col width="14" customWidth="1" min="7" max="7"/>
-    <col width="16" customWidth="1" min="8" max="8"/>
-    <col width="16" customWidth="1" min="9" max="9"/>
+    <col width="27" customWidth="1" min="8" max="8"/>
+    <col width="17" customWidth="1" min="9" max="9"/>
     <col width="19" customWidth="1" min="10" max="10"/>
     <col width="16" customWidth="1" min="11" max="11"/>
     <col width="15" customWidth="1" min="12" max="12"/>
@@ -700,7 +700,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>2 Years</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -710,12 +710,12 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>Graduation + CAT</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>CAT, GMAT, GRE</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -742,27 +742,27 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>MBA</t>
+          <t>Ph.D</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Master of Business Administration [MBA]</t>
+          <t>Ph.D. (Management)</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Master of Business Administration [MBA]</t>
+          <t>M.Phil/Ph.D in Management</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>20 Lakhs</t>
+          <t>Not Specified</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>3 Years</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -772,7 +772,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>Post Graduation + UGCNET</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -792,7 +792,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>PG</t>
+          <t>Doctorate</t>
         </is>
       </c>
     </row>
@@ -804,27 +804,27 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Ph.D</t>
+          <t>MBA</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Ph.D. (Management)</t>
+          <t>Post Graduate Programme in Management [PGPM]</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Ph.D. (Management)</t>
+          <t>Post Graduate Programme in Management [PGPM]</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>27.5 Lakhs</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>2 Years</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -834,12 +834,12 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>Graduation + CAT</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>CAT, GMAT, GRE</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -866,27 +866,27 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>MBA</t>
+          <t>Graduate Diploma in Education</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Post Graduate Programme in Management [PGPM]</t>
+          <t>Faculty Development Programme</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Post Graduate Programme in Management [PGPM]</t>
+          <t>Faculty Development Programme</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>27.5 Lakhs</t>
+          <t>1.38 Lakhs</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>1 Month</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -896,7 +896,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>Post Graduation</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -915,6 +915,68 @@
         </is>
       </c>
       <c r="L5" t="inlineStr">
+        <is>
+          <t>PG</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>25494</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Graduate Diploma in Management</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Armed Forces Programme</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Armed Forces Programme</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>6 Months</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Graduation</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
         <is>
           <t>PG</t>
         </is>
@@ -1025,7 +1087,7 @@
     <col width="18" customWidth="1" min="3" max="3"/>
     <col width="17" customWidth="1" min="4" max="4"/>
     <col width="23" customWidth="1" min="5" max="5"/>
-    <col width="73" customWidth="1" min="6" max="6"/>
+    <col width="17" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1068,17 +1130,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>1.15 CPA</t>
+          <t>1,10,00,000</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>35.07 LPA</t>
+          <t>35,22,591</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>36.2 LPA</t>
+          <t>34.59 LPA</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -1088,7 +1150,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Microsoft, Google, Accenture, TCS, Wipro, HCL, Goldman Sachs, Flipkart</t>
+          <t>Not Specified</t>
         </is>
       </c>
     </row>

--- a/exports/colleges/25494_iima-indian-institute-of-management-ahmedabad.xlsx
+++ b/exports/colleges/25494_iima-indian-institute-of-management-ahmedabad.xlsx
@@ -25,13 +25,16 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -42,7 +45,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -50,12 +53,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -441,72 +453,72 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>college_id</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>name</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>url</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>college_type</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>ownership</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>established_year</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>accreditation</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>affiliation</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>rating</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>ranking</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>city</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>state</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>overview_description</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>contact_info</t>
         </is>
@@ -593,15 +605,15 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L6"/>
+  <dimension ref="A1:L14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
-    <col width="33" customWidth="1" min="2" max="2"/>
+    <col width="47" customWidth="1" min="2" max="2"/>
     <col width="74" customWidth="1" min="3" max="3"/>
     <col width="74" customWidth="1" min="4" max="4"/>
-    <col width="16" customWidth="1" min="5" max="5"/>
-    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="25" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
     <col width="14" customWidth="1" min="7" max="7"/>
     <col width="27" customWidth="1" min="8" max="8"/>
     <col width="17" customWidth="1" min="9" max="9"/>
@@ -611,62 +623,62 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>college_id</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>degree_name</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>course_name</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>specialization</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>total_fees</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>duration</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>course_type</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>eligibility</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>entrance_exam</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>application_date</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>intake_seats</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>course_level</t>
         </is>
@@ -742,27 +754,27 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Ph.D</t>
+          <t>MBA</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Ph.D. (Management)</t>
+          <t>Post Graduate Program in Management for Executives [PGPX]</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>M.Phil/Ph.D in Management</t>
+          <t>Post Graduate Program in Management for Executives [PGPX]</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>34.5 Lakhs</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>3 Years</t>
+          <t>1 Year</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -772,12 +784,12 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Post Graduation + UGCNET</t>
+          <t>Graduation + GMAT/GRE</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>GMAT</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -792,7 +804,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>Doctorate</t>
+          <t>PG</t>
         </is>
       </c>
     </row>
@@ -809,17 +821,17 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Post Graduate Programme in Management [PGPM]</t>
+          <t>Master of Business Administration [MBA]</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Post Graduate Programme in Management [PGPM]</t>
+          <t>Master of Business Administration [MBA]</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>27.5 Lakhs</t>
+          <t>20 Lakhs</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -829,12 +841,12 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Full Time</t>
+          <t>Part Time</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Graduation + CAT</t>
+          <t>Graduation + GMAT</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -866,27 +878,27 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Graduate Diploma in Education</t>
+          <t>Ph.D</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Faculty Development Programme</t>
+          <t>Ph.D. (Management)</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Faculty Development Programme</t>
+          <t>M.Phil/Ph.D in Management</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>1.38 Lakhs</t>
+          <t>Not Specified</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>1 Month</t>
+          <t>3 Years</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -896,7 +908,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Post Graduation</t>
+          <t>Post Graduation + UGCNET</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -916,7 +928,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>PG</t>
+          <t>Doctorate</t>
         </is>
       </c>
     </row>
@@ -928,27 +940,27 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Graduate Diploma in Management</t>
+          <t>MBA</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Armed Forces Programme</t>
+          <t>Post Graduate Programme in Management [PGPM]</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Armed Forces Programme</t>
+          <t>Post Graduate Programme in Management [PGPM]</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>27.5 Lakhs</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>6 Months</t>
+          <t>2 Years</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -958,12 +970,12 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Graduation</t>
+          <t>Graduation + CAT</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>CAT, GMAT, GRE</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -979,6 +991,494 @@
       <c r="L6" t="inlineStr">
         <is>
           <t>PG</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>25494</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>PG Program</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>PG Program</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>PG Program</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>20 Lakhs - 71.2 Lakhs</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>UG</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>25494</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>MBA</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>PGPX</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>PGPX</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>12 Lakhs - 35.35 Lakhs</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>2 Years</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Part Time</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>CAT</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>PG</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>25494</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>FDP</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>FDP</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>FDP</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>1.38 Lakhs</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>UG</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>25494</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Certification</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Certification</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Certification</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>11.88 Lakhs</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>UG</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>25494</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>PG Program Food And Agri-Business Management</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>PG Program Food And Agri-Business Management</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>PG Program Food And Agri-Business Management</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>27.5 Lakhs</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>UG</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>25494</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>MBA</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>PGPM General</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>PGPM General</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>27.5 Lakhs</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>2 Years</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>CAT</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>PG</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>25494</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>FDP</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>FDP (General)</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>General</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>1.38 Lakhs</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr"/>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>UG</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>25494</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Certification</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Certification (General)</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>General</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>11.88 Lakhs</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr"/>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>UG</t>
         </is>
       </c>
     </row>
@@ -1005,32 +1505,32 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>college_id</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>admission_process</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>exams_accepted</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>eligibility_criteria</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>important_dates</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>application_deadlines</t>
         </is>
@@ -1091,32 +1591,32 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>college_id</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>highest_package</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>average_package</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>median_package</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>placement_percentage</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>top_recruiters</t>
         </is>
@@ -1145,7 +1645,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -1175,22 +1675,22 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>college_id</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>ranking_body</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>rank</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>ranking_year</t>
         </is>
@@ -1233,12 +1733,12 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>college_id</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>status</t>
         </is>
@@ -1275,12 +1775,12 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>college_id</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>status</t>
         </is>
@@ -1318,17 +1818,17 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>college_id</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>hostel_fees</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>facilities</t>
         </is>
@@ -1372,22 +1872,22 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>college_id</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>reviewer_name</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>rating</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>review_text</t>
         </is>

--- a/exports/colleges/25494_iima-indian-institute-of-management-ahmedabad.xlsx
+++ b/exports/colleges/25494_iima-indian-institute-of-management-ahmedabad.xlsx
@@ -1866,9 +1866,9 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
-    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
     <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="90" customWidth="1" min="4" max="4"/>
+    <col width="449" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1901,7 +1901,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Aditya Sharma</t>
+          <t>Alumni Reviewer</t>
         </is>
       </c>
       <c r="C2" t="n">
@@ -1909,7 +1909,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Excellent academic atmosphere, world class research facilities, and amazing placements.</t>
+          <t>Pros: The PGP program offered here is the flagship program of this institute and one of the best in the world. Internships are a compulsory part of an MBA curriculum; every student gets an internship from within the campus. Companies conduct a GD/PI process to select the best candidates. All the top-notch companies from the areas of consulting, investment banking, and FMCG come for the placements. Salary figures in this industry are the best.</t>
         </is>
       </c>
     </row>

--- a/exports/colleges/25494_iima-indian-institute-of-management-ahmedabad.xlsx
+++ b/exports/colleges/25494_iima-indian-institute-of-management-ahmedabad.xlsx
@@ -570,7 +570,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>CD Rank #2</t>
+          <t>Not Ranked</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -605,7 +605,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L14"/>
+  <dimension ref="A1:L19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -617,7 +617,7 @@
     <col width="14" customWidth="1" min="7" max="7"/>
     <col width="27" customWidth="1" min="8" max="8"/>
     <col width="17" customWidth="1" min="9" max="9"/>
-    <col width="19" customWidth="1" min="10" max="10"/>
+    <col width="24" customWidth="1" min="10" max="10"/>
     <col width="16" customWidth="1" min="11" max="11"/>
     <col width="15" customWidth="1" min="12" max="12"/>
   </cols>
@@ -707,12 +707,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>27.5 Lakhs</t>
+          <t>27.5 L</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2 Years</t>
+          <t>2 years</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -722,17 +722,17 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Graduation + CAT</t>
+          <t>Not Specified</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>CAT, GMAT, GRE</t>
+          <t>CAT</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>1 Aug - 13 Sept 2026</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -769,32 +769,32 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>34.5 Lakhs</t>
+          <t>34.5 L</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>1 Year</t>
+          <t>1 year</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Full Time</t>
+          <t>Part Time</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Graduation + GMAT/GRE</t>
+          <t>Not Specified</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>GMAT</t>
+          <t>CAT</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>7 July - 08 Sept 2026</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -831,12 +831,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>20 Lakhs</t>
+          <t>20 L</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2 Years</t>
+          <t>2 years</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -846,12 +846,12 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Graduation + GMAT</t>
+          <t>Not Specified</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>CAT, GMAT, GRE</t>
+          <t>CAT</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -888,7 +888,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>M.Phil/Ph.D in Management</t>
+          <t>Ph.D. (Management)</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>3 Years</t>
+          <t>3 years</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -908,17 +908,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Post Graduation + UGCNET</t>
+          <t>Not Specified</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>GATE / UGC NET</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>15 Jan - 31 Jan 2026</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -955,12 +955,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>27.5 Lakhs</t>
+          <t>27.5 L</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2 Years</t>
+          <t>2 years</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -970,17 +970,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Graduation + CAT</t>
+          <t>Not Specified</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>CAT, GMAT, GRE</t>
+          <t>CAT</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>1 Aug - 13 Sept 2026</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1002,27 +1002,27 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>PG Program</t>
+          <t>MBA</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>PG Program</t>
+          <t>Post Graduate Programme in Food and Agri-Business Management [PGP-FABM]</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>PG Program</t>
+          <t>Post Graduate Programme in Food and Agri-Business Management [PGP-FABM]</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>20 Lakhs - 71.2 Lakhs</t>
+          <t>27.5 Lakhs</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>2 Years</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -1032,12 +1032,12 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>Graduation + CAT</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>CAT, GMAT, GRE</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1052,7 +1052,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>UG</t>
+          <t>PG</t>
         </is>
       </c>
     </row>
@@ -1069,37 +1069,37 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>PGPX</t>
+          <t>Post Graduate Program in Management for Executives [PGPX]</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>PGPX</t>
+          <t>Post Graduate Program in Management for Executives [PGPX]</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>12 Lakhs - 35.35 Lakhs</t>
+          <t>34.5 Lakhs</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2 Years</t>
+          <t>1 Year</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Part Time</t>
+          <t>Full Time</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>Graduation + GMAT/GRE</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>CAT</t>
+          <t>GMAT</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1126,42 +1126,42 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>FDP</t>
+          <t>MBA</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>FDP</t>
+          <t>Master of Business Administration [MBA]</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>FDP</t>
+          <t>Master of Business Administration [MBA]</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>1.38 Lakhs</t>
+          <t>20 Lakhs</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>2 Years</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Full Time</t>
+          <t>Part Time</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>Graduation + GMAT</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>CAT, GMAT, GRE</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1176,7 +1176,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>UG</t>
+          <t>PG</t>
         </is>
       </c>
     </row>
@@ -1188,27 +1188,27 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Certification</t>
+          <t>Ph.D</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Certification</t>
+          <t>Ph.D. (Management)</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Certification</t>
+          <t>M.Phil/Ph.D in Management</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>11.88 Lakhs</t>
+          <t>Not Specified</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>3 Years</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -1218,7 +1218,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>Post Graduation + UGCNET</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1238,7 +1238,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>UG</t>
+          <t>Doctorate</t>
         </is>
       </c>
     </row>
@@ -1250,17 +1250,17 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>PG Program Food And Agri-Business Management</t>
+          <t>MBA</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>PG Program Food And Agri-Business Management</t>
+          <t>Post Graduate Programme in Management [PGPM]</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>PG Program Food And Agri-Business Management</t>
+          <t>Post Graduate Programme in Management [PGPM]</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -1270,7 +1270,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>2 Years</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -1280,12 +1280,12 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>Graduation + CAT</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>CAT, GMAT, GRE</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1300,7 +1300,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>UG</t>
+          <t>PG</t>
         </is>
       </c>
     </row>
@@ -1312,27 +1312,27 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>MBA</t>
+          <t>PG Program</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>PGPM General</t>
+          <t>PG Program</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>PGPM General</t>
+          <t>PG Program</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>27.5 Lakhs</t>
+          <t>20 Lakhs - 71.2 Lakhs</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2 Years</t>
+          <t>Not Specified</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -1347,7 +1347,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>CAT</t>
+          <t>Not Specified</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1362,7 +1362,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>PG</t>
+          <t>UG</t>
         </is>
       </c>
     </row>
@@ -1374,28 +1374,32 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>FDP</t>
+          <t>MBA</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>FDP (General)</t>
+          <t>PGPX</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>General</t>
+          <t>PGPX</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>1.38 Lakhs</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr"/>
+          <t>12 Lakhs - 35.35 Lakhs</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>2 Years</t>
+        </is>
+      </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Full Time</t>
+          <t>Part Time</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1405,7 +1409,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>CAT</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -1420,7 +1424,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>UG</t>
+          <t>PG</t>
         </is>
       </c>
     </row>
@@ -1432,51 +1436,357 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
+          <t>FDP</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>FDP</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>FDP</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>1.38 Lakhs</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>UG</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>25494</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
           <t>Certification</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr">
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Certification</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Certification</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>11.88 Lakhs</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>UG</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>25494</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>PG Program Food And Agri-Business Management</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>PG Program Food And Agri-Business Management</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>PG Program Food And Agri-Business Management</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>27.5 Lakhs</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>UG</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>25494</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>MBA</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>PGPM General</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>PGPM General</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>27.5 Lakhs</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>2 Years</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>CAT</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>PG</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>25494</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>FDP</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>FDP (General)</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>General</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>1.38 Lakhs</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr"/>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>UG</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>25494</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Certification</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
         <is>
           <t>Certification (General)</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr">
+      <c r="D19" t="inlineStr">
         <is>
           <t>General</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr">
+      <c r="E19" t="inlineStr">
         <is>
           <t>11.88 Lakhs</t>
         </is>
       </c>
-      <c r="F14" t="inlineStr"/>
-      <c r="G14" t="inlineStr">
+      <c r="F19" t="inlineStr"/>
+      <c r="G19" t="inlineStr">
         <is>
           <t>Full Time</t>
         </is>
       </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>Not Specified</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>Not Specified</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>Not Specified</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>Not Specified</t>
-        </is>
-      </c>
-      <c r="L14" t="inlineStr">
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
         <is>
           <t>UG</t>
         </is>
@@ -1630,12 +1940,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>1,10,00,000</t>
+          <t>Not Specified</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>35,22,591</t>
+          <t>Not Specified</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -1645,7 +1955,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>Not Specified</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -1670,7 +1980,7 @@
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
     <col width="15" customWidth="1" min="2" max="2"/>
-    <col width="13" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
     <col width="15" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
@@ -1709,10 +2019,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>CD Rank #2</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr"/>
+          <t>#1</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>2025</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/exports/colleges/25494_iima-indian-institute-of-management-ahmedabad.xlsx
+++ b/exports/colleges/25494_iima-indian-institute-of-management-ahmedabad.xlsx
@@ -570,7 +570,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>Not Ranked</t>
+          <t>CD Rank #2</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -605,19 +605,19 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L19"/>
+  <dimension ref="A1:L6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
-    <col width="47" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
     <col width="74" customWidth="1" min="3" max="3"/>
     <col width="74" customWidth="1" min="4" max="4"/>
-    <col width="25" customWidth="1" min="5" max="5"/>
-    <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
     <col width="14" customWidth="1" min="7" max="7"/>
     <col width="27" customWidth="1" min="8" max="8"/>
     <col width="17" customWidth="1" min="9" max="9"/>
-    <col width="24" customWidth="1" min="10" max="10"/>
+    <col width="19" customWidth="1" min="10" max="10"/>
     <col width="16" customWidth="1" min="11" max="11"/>
     <col width="15" customWidth="1" min="12" max="12"/>
   </cols>
@@ -707,12 +707,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>27.5 L</t>
+          <t>27.5 Lakhs</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2 years</t>
+          <t>2 Years</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -722,17 +722,17 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>Graduation + CAT</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>CAT</t>
+          <t>CAT, GMAT, GRE</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>1 Aug - 13 Sept 2026</t>
+          <t>Not Specified</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -759,42 +759,42 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Post Graduate Program in Management for Executives [PGPX]</t>
+          <t>Post Graduate Programme in Management for Executives [PGPX]</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Post Graduate Program in Management for Executives [PGPX]</t>
+          <t>Post Graduate Programme in Management for Executives [PGPX]</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>34.5 L</t>
+          <t>34.5 Lakhs</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>1 year</t>
+          <t>1 Year</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Part Time</t>
+          <t>Full Time</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>Graduation + GMAT/GRE</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>CAT</t>
+          <t>GMAT</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>7 July - 08 Sept 2026</t>
+          <t>Not Specified</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -831,12 +831,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>20 L</t>
+          <t>20 Lakhs</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2 years</t>
+          <t>2 Years</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -846,12 +846,12 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>Graduation + GMAT</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>CAT</t>
+          <t>CAT, GMAT, GRE</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -888,7 +888,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Ph.D. (Management)</t>
+          <t>M.Phil/Ph.D in Management</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>3 years</t>
+          <t>3 Years</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -908,17 +908,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>Post Graduation + UGCNET</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>GATE / UGC NET</t>
+          <t>Not Specified</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>15 Jan - 31 Jan 2026</t>
+          <t>Not Specified</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -955,12 +955,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>27.5 L</t>
+          <t>27.5 Lakhs</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2 years</t>
+          <t>2 Years</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -970,17 +970,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>Graduation + CAT</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>CAT</t>
+          <t>CAT, GMAT, GRE</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>1 Aug - 13 Sept 2026</t>
+          <t>Not Specified</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -991,804 +991,6 @@
       <c r="L6" t="inlineStr">
         <is>
           <t>PG</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>25494</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>MBA</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Post Graduate Programme in Food and Agri-Business Management [PGP-FABM]</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>Post Graduate Programme in Food and Agri-Business Management [PGP-FABM]</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>27.5 Lakhs</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>2 Years</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>Full Time</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>Graduation + CAT</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>CAT, GMAT, GRE</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>Not Specified</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>Not Specified</t>
-        </is>
-      </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>PG</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>25494</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>MBA</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Post Graduate Program in Management for Executives [PGPX]</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>Post Graduate Program in Management for Executives [PGPX]</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>34.5 Lakhs</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>1 Year</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>Full Time</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>Graduation + GMAT/GRE</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>GMAT</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>Not Specified</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>Not Specified</t>
-        </is>
-      </c>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>PG</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>25494</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>MBA</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Master of Business Administration [MBA]</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>Master of Business Administration [MBA]</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>20 Lakhs</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>2 Years</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>Part Time</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>Graduation + GMAT</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>CAT, GMAT, GRE</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>Not Specified</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>Not Specified</t>
-        </is>
-      </c>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>PG</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>25494</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>Ph.D</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ph.D. (Management)</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>M.Phil/Ph.D in Management</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>Not Specified</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>3 Years</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>Full Time</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>Post Graduation + UGCNET</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>Not Specified</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>Not Specified</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>Not Specified</t>
-        </is>
-      </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>Doctorate</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>25494</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>MBA</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Post Graduate Programme in Management [PGPM]</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>Post Graduate Programme in Management [PGPM]</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>27.5 Lakhs</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>2 Years</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>Full Time</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>Graduation + CAT</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>CAT, GMAT, GRE</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>Not Specified</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>Not Specified</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>PG</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>25494</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>PG Program</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>PG Program</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>PG Program</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>20 Lakhs - 71.2 Lakhs</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>Not Specified</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>Full Time</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>Not Specified</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>Not Specified</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>Not Specified</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>Not Specified</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>UG</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>25494</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>MBA</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>PGPX</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>PGPX</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>12 Lakhs - 35.35 Lakhs</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>2 Years</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>Part Time</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>Not Specified</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>CAT</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>Not Specified</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>Not Specified</t>
-        </is>
-      </c>
-      <c r="L13" t="inlineStr">
-        <is>
-          <t>PG</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>25494</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>FDP</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>FDP</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>FDP</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>1.38 Lakhs</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>Not Specified</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>Full Time</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>Not Specified</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>Not Specified</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>Not Specified</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>Not Specified</t>
-        </is>
-      </c>
-      <c r="L14" t="inlineStr">
-        <is>
-          <t>UG</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>25494</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>Certification</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Certification</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>Certification</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>11.88 Lakhs</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>Not Specified</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>Full Time</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>Not Specified</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>Not Specified</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>Not Specified</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>Not Specified</t>
-        </is>
-      </c>
-      <c r="L15" t="inlineStr">
-        <is>
-          <t>UG</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>25494</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>PG Program Food And Agri-Business Management</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>PG Program Food And Agri-Business Management</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>PG Program Food And Agri-Business Management</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>27.5 Lakhs</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>Not Specified</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>Full Time</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>Not Specified</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>Not Specified</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>Not Specified</t>
-        </is>
-      </c>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>Not Specified</t>
-        </is>
-      </c>
-      <c r="L16" t="inlineStr">
-        <is>
-          <t>UG</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>25494</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>MBA</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>PGPM General</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>PGPM General</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>27.5 Lakhs</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>2 Years</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>Full Time</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>Not Specified</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>CAT</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>Not Specified</t>
-        </is>
-      </c>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>Not Specified</t>
-        </is>
-      </c>
-      <c r="L17" t="inlineStr">
-        <is>
-          <t>PG</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>25494</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>FDP</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>FDP (General)</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>General</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>1.38 Lakhs</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr"/>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>Full Time</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>Not Specified</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>Not Specified</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>Not Specified</t>
-        </is>
-      </c>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>Not Specified</t>
-        </is>
-      </c>
-      <c r="L18" t="inlineStr">
-        <is>
-          <t>UG</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>25494</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>Certification</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Certification (General)</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>General</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>11.88 Lakhs</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr"/>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>Full Time</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>Not Specified</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>Not Specified</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>Not Specified</t>
-        </is>
-      </c>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>Not Specified</t>
-        </is>
-      </c>
-      <c r="L19" t="inlineStr">
-        <is>
-          <t>UG</t>
         </is>
       </c>
     </row>
@@ -1940,22 +1142,22 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>1.10 Cr</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>35.23 LPA</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>34.59 LPA</t>
+          <t>34.53 Lakh</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -1980,7 +1182,7 @@
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
     <col width="15" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
     <col width="15" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
@@ -2019,12 +1221,10 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>#1</t>
-        </is>
-      </c>
-      <c r="D2" t="n">
-        <v>2025</v>
-      </c>
+          <t>CD Rank #2</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
